--- a/data/trans_dic/P19D_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19D_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,48; 97,63</t>
+          <t>91,46; 97,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,87; 89,13</t>
+          <t>79,53; 88,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,85; 90,85</t>
+          <t>81,35; 90,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87,22; 96,54</t>
+          <t>89,81; 96,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,26; 97,52</t>
+          <t>91,37; 97,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,58; 90,12</t>
+          <t>79,98; 89,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,4; 90,75</t>
+          <t>81,92; 90,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,27; 98,09</t>
+          <t>95,23; 98,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,53; 96,86</t>
+          <t>92,45; 96,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81,23; 88,05</t>
+          <t>81,71; 88,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83,61; 89,63</t>
+          <t>83,25; 89,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,09; 96,81</t>
+          <t>93,34; 96,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,36; 91,81</t>
+          <t>85,38; 91,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,07; 85,61</t>
+          <t>76,7; 85,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92,01; 96,59</t>
+          <t>91,99; 96,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,2; 95,1</t>
+          <t>88,13; 95,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,26; 93,14</t>
+          <t>87,67; 92,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,53; 90,88</t>
+          <t>84,39; 90,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,31; 97,1</t>
+          <t>92,45; 97,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,76; 96,53</t>
+          <t>92,76; 96,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,71; 91,81</t>
+          <t>87,13; 91,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81,89; 87,17</t>
+          <t>82,04; 86,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93,16; 96,4</t>
+          <t>93,21; 96,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,87; 95,39</t>
+          <t>91,96; 95,73</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,12; 95,89</t>
+          <t>89,35; 95,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,67; 88,11</t>
+          <t>80,29; 88,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,22; 94,55</t>
+          <t>88,63; 94,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91,81; 96,54</t>
+          <t>91,86; 96,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,16; 96,62</t>
+          <t>90,95; 96,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,98; 89,04</t>
+          <t>81,2; 89,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,97; 94,11</t>
+          <t>88,11; 94,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,92; 96,99</t>
+          <t>93,07; 96,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,45; 95,67</t>
+          <t>91,51; 95,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82,17; 87,59</t>
+          <t>81,81; 87,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,15; 93,5</t>
+          <t>89,37; 93,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>93,41; 96,29</t>
+          <t>93,16; 96,09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,26; 95,87</t>
+          <t>89,57; 95,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,65; 91,79</t>
+          <t>83,82; 91,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,79; 91,95</t>
+          <t>84,15; 91,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92,26; 98,39</t>
+          <t>92,18; 98,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,53; 96,65</t>
+          <t>91,59; 96,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,39; 93,59</t>
+          <t>87,7; 93,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,17; 94,45</t>
+          <t>87,7; 94,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>96,66; 98,92</t>
+          <t>95,96; 98,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,58; 95,59</t>
+          <t>91,41; 95,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86,98; 91,91</t>
+          <t>87,02; 91,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87,74; 92,45</t>
+          <t>87,6; 92,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,56; 98,43</t>
+          <t>94,86; 98,07</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>88,24; 96,56</t>
+          <t>88,92; 96,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81,22; 90,96</t>
+          <t>80,61; 90,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,08; 95,34</t>
+          <t>85,82; 95,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,65; 96,1</t>
+          <t>88,13; 94,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,5; 95,58</t>
+          <t>86,88; 95,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,82; 91,82</t>
+          <t>82,08; 91,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,88; 91,7</t>
+          <t>80,93; 92,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,37; 96,34</t>
+          <t>91,17; 95,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89,27; 95,04</t>
+          <t>89,66; 95,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83,17; 89,84</t>
+          <t>83,13; 89,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85,11; 92,45</t>
+          <t>84,78; 92,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>92,32; 95,59</t>
+          <t>90,61; 94,65</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,29; 96,85</t>
+          <t>89,45; 96,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,69; 88,91</t>
+          <t>79,83; 89,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,59; 93,35</t>
+          <t>85,51; 93,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91,49; 96,33</t>
+          <t>91,18; 96,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,13; 97,69</t>
+          <t>92,11; 98,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,09; 90,13</t>
+          <t>81,15; 89,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,94; 95,27</t>
+          <t>88,4; 95,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91,5; 96,1</t>
+          <t>90,96; 95,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92,04; 96,69</t>
+          <t>92,02; 96,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82,01; 88,38</t>
+          <t>82,31; 88,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>88,28; 93,63</t>
+          <t>88,35; 93,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>92,16; 95,54</t>
+          <t>92,01; 95,59</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,91; 94,66</t>
+          <t>89,88; 94,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>84,77; 90,54</t>
+          <t>85,05; 90,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,22; 93,91</t>
+          <t>88,4; 93,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90,85; 96,17</t>
+          <t>90,66; 95,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,96; 95,28</t>
+          <t>90,66; 95,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,62; 93,28</t>
+          <t>88,5; 93,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,37; 93,11</t>
+          <t>87,67; 93,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>93,94; 98,12</t>
+          <t>93,21; 96,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,44; 94,55</t>
+          <t>91,12; 94,43</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87,55; 91,26</t>
+          <t>87,58; 91,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88,83; 92,96</t>
+          <t>89,12; 93,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,55; 97,11</t>
+          <t>92,56; 95,43</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>91,3; 95,53</t>
+          <t>91,47; 95,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,47; 91,97</t>
+          <t>86,63; 91,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,98; 91,76</t>
+          <t>86,86; 92,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,94; 84,8</t>
+          <t>80,48; 85,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>89,57; 94,15</t>
+          <t>89,42; 94,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,16; 93,5</t>
+          <t>89,22; 93,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,22; 92,63</t>
+          <t>88,15; 92,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86,79; 91,55</t>
+          <t>87,93; 91,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91,02; 94,26</t>
+          <t>91,07; 94,23</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88,61; 92,14</t>
+          <t>88,61; 92,07</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88,57; 91,77</t>
+          <t>88,42; 91,6</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>45,61; 87,4</t>
+          <t>84,99; 88,26</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>91,65; 93,72</t>
+          <t>91,57; 93,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>85,06; 87,7</t>
+          <t>84,89; 87,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89,4; 91,77</t>
+          <t>89,51; 91,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63,3; 92,13</t>
+          <t>90,32; 92,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>92,04; 93,99</t>
+          <t>91,98; 93,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>87,88; 90,11</t>
+          <t>87,81; 90,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90,05; 92,15</t>
+          <t>90,06; 92,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>93,78; 95,73</t>
+          <t>93,44; 94,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92,14; 93,52</t>
+          <t>92,12; 93,6</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86,92; 88,65</t>
+          <t>86,78; 88,58</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90,17; 91,64</t>
+          <t>90,02; 91,61</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>78,5; 93,64</t>
+          <t>92,17; 93,49</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>285599</t>
+          <t>282271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>278659</t>
+          <t>300284</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>564258</t>
+          <t>582555</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>175187; 186957</t>
+          <t>175146; 187007</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>200112; 223324</t>
+          <t>199282; 222430</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>200702; 222776</t>
+          <t>199493; 222278</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266396; 294869</t>
+          <t>270254; 289636</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>183642; 196222</t>
+          <t>183862; 196055</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>202443; 226401</t>
+          <t>200934; 225434</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>202977; 223556</t>
+          <t>201805; 223721</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>274011; 282128</t>
+          <t>294709; 304012</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>363373; 380381</t>
+          <t>363061; 380521</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>407605; 441829</t>
+          <t>410006; 442532</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>410969; 440567</t>
+          <t>409220; 440579</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>540193; 574143</t>
+          <t>569701; 590595</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>469964</t>
+          <t>483215</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>479344</t>
+          <t>508476</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>949308</t>
+          <t>991691</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>349748; 376184</t>
+          <t>349842; 376405</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>313170; 347842</t>
+          <t>311642; 345822</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>334139; 350788</t>
+          <t>334067; 351020</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>445199; 485532</t>
+          <t>459560; 498074</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>384973; 410931</t>
+          <t>386794; 409680</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>370018; 397809</t>
+          <t>369419; 396825</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>363090; 381913</t>
+          <t>363617; 381790</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>467541; 486557</t>
+          <t>495501; 515855</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>746381; 781272</t>
+          <t>741472; 779111</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>691182; 735756</t>
+          <t>692499; 734204</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>704777; 729269</t>
+          <t>705098; 728635</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>921982; 967825</t>
+          <t>970721; 1010524</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>288298</t>
+          <t>286992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>320623</t>
+          <t>325811</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>608921</t>
+          <t>612802</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>210799; 226823</t>
+          <t>211353; 227033</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>233217; 257931</t>
+          <t>235048; 259704</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>256285; 274669</t>
+          <t>257489; 274775</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>279865; 294293</t>
+          <t>279095; 293289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>263280; 279053</t>
+          <t>262666; 278124</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>266238; 292736</t>
+          <t>266955; 293194</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>270742; 289631</t>
+          <t>271156; 289312</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>312559; 326236</t>
+          <t>318388; 331619</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>480439; 502580</t>
+          <t>480753; 501728</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>510684; 544344</t>
+          <t>508451; 545639</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>533335; 559365</t>
+          <t>534684; 560249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>598983; 617393</t>
+          <t>601736; 620711</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298514</t>
+          <t>357447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>464237</t>
+          <t>409033</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>762751</t>
+          <t>766479</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>238802; 256471</t>
+          <t>239617; 256486</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>260271; 285594</t>
+          <t>260806; 284369</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>279837; 303481</t>
+          <t>277739; 303108</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>286131; 305115</t>
+          <t>341743; 364918</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>274154; 289486</t>
+          <t>274333; 290077</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>297994; 319106</t>
+          <t>299048; 319315</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>307599; 329500</t>
+          <t>305947; 328610</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>457650; 468331</t>
+          <t>402668; 413151</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>519313; 542045</t>
+          <t>518331; 542435</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>567191; 599342</t>
+          <t>567475; 598829</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>595668; 627623</t>
+          <t>594711; 627231</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>748808; 771256</t>
+          <t>749714; 775074</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157922</t>
+          <t>174121</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>191157</t>
+          <t>205903</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>349080</t>
+          <t>380025</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>150255; 164414</t>
+          <t>151418; 164092</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>156751; 175548</t>
+          <t>155570; 175109</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101431; 113666</t>
+          <t>102318; 113741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>152688; 161855</t>
+          <t>166821; 179252</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>150433; 166228</t>
+          <t>151086; 166445</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>161080; 178580</t>
+          <t>159641; 178496</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>117684; 133428</t>
+          <t>117748; 134410</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>186853; 194880</t>
+          <t>200383; 209939</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>307249; 327122</t>
+          <t>308612; 327790</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>322278; 348114</t>
+          <t>322112; 348179</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>225293; 244746</t>
+          <t>224437; 244774</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>342250; 354369</t>
+          <t>370694; 387202</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239376</t>
+          <t>234767</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>232554</t>
+          <t>236647</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>471931</t>
+          <t>471413</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>169008; 183309</t>
+          <t>169296; 183443</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>198376; 221342</t>
+          <t>198729; 221931</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>199948; 218076</t>
+          <t>199772; 218642</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>232313; 244595</t>
+          <t>227220; 240134</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>188389; 199760</t>
+          <t>188358; 200434</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>214745; 238679</t>
+          <t>214917; 236721</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>219815; 235452</t>
+          <t>218481; 235422</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>225999; 237360</t>
+          <t>229374; 241609</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>362432; 380717</t>
+          <t>362348; 381136</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>421332; 454060</t>
+          <t>422862; 454621</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>424421; 450120</t>
+          <t>424757; 450235</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>461646; 478583</t>
+          <t>461311; 479241</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>557632</t>
+          <t>644154</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>794092</t>
+          <t>701927</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1351725</t>
+          <t>1346082</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>418218; 440307</t>
+          <t>418083; 440476</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>487364; 520576</t>
+          <t>488998; 521726</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>389285; 414385</t>
+          <t>390091; 414492</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>538751; 570308</t>
+          <t>624876; 658270</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>490632; 513931</t>
+          <t>488988; 513187</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>554062; 583181</t>
+          <t>553273; 582869</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>424448; 452290</t>
+          <t>425884; 453055</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>777220; 811782</t>
+          <t>689776; 712957</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>918536; 949761</t>
+          <t>915377; 948585</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1050710; 1095210</t>
+          <t>1051061; 1096814</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>823497; 861809</t>
+          <t>826220; 862649</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1328814; 1379259</t>
+          <t>1322883; 1363844</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>557543</t>
+          <t>642904</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>631568</t>
+          <t>729060</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1189111</t>
+          <t>1371963</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>481199; 503497</t>
+          <t>482110; 504498</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>544626; 579308</t>
+          <t>545620; 578926</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>556066; 586651</t>
+          <t>555324; 589430</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>235582; 769972</t>
+          <t>620031; 661298</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>530625; 557729</t>
+          <t>529756; 557314</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>624360; 654783</t>
+          <t>624758; 653396</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>609909; 640418</t>
+          <t>609428; 640248</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>611767; 645312</t>
+          <t>713175; 743062</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1018951; 1055196</t>
+          <t>1019542; 1054914</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1178651; 1225601</t>
+          <t>1178596; 1224680</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1178530; 1221173</t>
+          <t>1176545; 1218892</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>735581; 1409629</t>
+          <t>1344046; 1395836</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2854849</t>
+          <t>3105870</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3392236</t>
+          <t>3417140</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6247085</t>
+          <t>6523010</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2251886; 2302857</t>
+          <t>2249837; 2300234</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2473137; 2549828</t>
+          <t>2468125; 2545943</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2380281; 2443382</t>
+          <t>2383071; 2443180</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2123195; 3090183</t>
+          <t>3066293; 3138379</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2522663; 2576218</t>
+          <t>2521152; 2574645</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2762378; 2832521</t>
+          <t>2760393; 2831392</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2580896; 2641074</t>
+          <t>2581069; 2641585</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3360304; 3429908</t>
+          <t>3390242; 3440254</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4789258; 4861204</t>
+          <t>4788556; 4865565</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5259369; 5364415</t>
+          <t>5250889; 5360122</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4985241; 5066508</t>
+          <t>4976550; 5064315</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5446122; 6496025</t>
+          <t>6473295; 6566293</t>
         </is>
       </c>
     </row>
